--- a/artfynd/A 50435-2024 artfynd.xlsx
+++ b/artfynd/A 50435-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,6 +785,238 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>124090043</v>
+      </c>
+      <c r="B3" t="n">
+        <v>103506</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sydost om Stensta, Brobyborg, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>683552</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6616649</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124092317</v>
+      </c>
+      <c r="B4" t="n">
+        <v>103506</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>N Brobyborg, Brobyborg, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>683540</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6616608</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50435-2024 artfynd.xlsx
+++ b/artfynd/A 50435-2024 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124545129</v>
+        <v>124547663</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1058,24 +1058,31 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stensta, Brobyborg, Upl</t>
+          <t>Barrskog S om Stensta, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683517</v>
+        <v>683503</v>
       </c>
       <c r="R5" t="n">
-        <v>6616645</v>
+        <v>6616418</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124545084</v>
+        <v>124545129</v>
       </c>
       <c r="B6" t="n">
-        <v>57761</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,21 +1154,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103012</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1180,13 +1187,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683542</v>
+        <v>683517</v>
       </c>
       <c r="R6" t="n">
-        <v>6616641</v>
+        <v>6616645</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1242,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124547663</v>
+        <v>124545084</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>57761</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,25 +1261,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>103012</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1280,28 +1287,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Barrskog S om Stensta, Brobyborg, Upl</t>
+          <t>Stensta, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>683503</v>
+        <v>683542</v>
       </c>
       <c r="R7" t="n">
-        <v>6616418</v>
+        <v>6616641</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 50435-2024 artfynd.xlsx
+++ b/artfynd/A 50435-2024 artfynd.xlsx
@@ -788,7 +788,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124092317</v>
+        <v>124090043</v>
       </c>
       <c r="B3" t="n">
         <v>103528</v>
@@ -833,19 +833,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>N Brobyborg, Brobyborg, Upl</t>
+          <t>Sydost om Stensta, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>683540</v>
+        <v>683552</v>
       </c>
       <c r="R3" t="n">
-        <v>6616608</v>
+        <v>6616649</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124090043</v>
+        <v>124092317</v>
       </c>
       <c r="B4" t="n">
         <v>103528</v>
@@ -949,19 +949,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sydost om Stensta, Brobyborg, Upl</t>
+          <t>N Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683552</v>
+        <v>683540</v>
       </c>
       <c r="R4" t="n">
-        <v>6616649</v>
+        <v>6616608</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124547663</v>
+        <v>124545084</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>57761</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1058,28 +1058,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Barrskog S om Stensta, Brobyborg, Upl</t>
+          <t>Stensta, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683503</v>
+        <v>683542</v>
       </c>
       <c r="R5" t="n">
-        <v>6616418</v>
+        <v>6616641</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1138,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124545129</v>
+        <v>124547663</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,25 +1143,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1176,24 +1169,31 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stensta, Brobyborg, Upl</t>
+          <t>Barrskog S om Stensta, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683517</v>
+        <v>683503</v>
       </c>
       <c r="R6" t="n">
-        <v>6616645</v>
+        <v>6616418</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124545084</v>
+        <v>124545129</v>
       </c>
       <c r="B7" t="n">
-        <v>57761</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,21 +1265,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103012</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1298,13 +1298,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>683542</v>
+        <v>683517</v>
       </c>
       <c r="R7" t="n">
-        <v>6616641</v>
+        <v>6616645</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 50435-2024 artfynd.xlsx
+++ b/artfynd/A 50435-2024 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124545084</v>
+        <v>124545129</v>
       </c>
       <c r="B5" t="n">
-        <v>57761</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683542</v>
+        <v>683517</v>
       </c>
       <c r="R5" t="n">
-        <v>6616641</v>
+        <v>6616645</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124547663</v>
+        <v>124545084</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>57761</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,25 +1143,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1169,28 +1169,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Barrskog S om Stensta, Brobyborg, Upl</t>
+          <t>Stensta, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683503</v>
+        <v>683542</v>
       </c>
       <c r="R6" t="n">
-        <v>6616418</v>
+        <v>6616641</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124545129</v>
+        <v>124547663</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,25 +1254,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1287,24 +1280,31 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stensta, Brobyborg, Upl</t>
+          <t>Barrskog S om Stensta, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>683517</v>
+        <v>683503</v>
       </c>
       <c r="R7" t="n">
-        <v>6616645</v>
+        <v>6616418</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 50435-2024 artfynd.xlsx
+++ b/artfynd/A 50435-2024 artfynd.xlsx
@@ -788,7 +788,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124090043</v>
+        <v>124092317</v>
       </c>
       <c r="B3" t="n">
         <v>103528</v>
@@ -833,19 +833,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sydost om Stensta, Brobyborg, Upl</t>
+          <t>N Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>683552</v>
+        <v>683540</v>
       </c>
       <c r="R3" t="n">
-        <v>6616649</v>
+        <v>6616608</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124092317</v>
+        <v>124090043</v>
       </c>
       <c r="B4" t="n">
         <v>103528</v>
@@ -949,19 +949,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>N Brobyborg, Brobyborg, Upl</t>
+          <t>Sydost om Stensta, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683540</v>
+        <v>683552</v>
       </c>
       <c r="R4" t="n">
-        <v>6616608</v>
+        <v>6616649</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124547663</v>
+        <v>124545084</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>57761</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1058,28 +1058,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Barrskog S om Stensta, Brobyborg, Upl</t>
+          <t>Stensta, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683503</v>
+        <v>683542</v>
       </c>
       <c r="R5" t="n">
-        <v>6616418</v>
+        <v>6616641</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1249,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124545084</v>
+        <v>124547663</v>
       </c>
       <c r="B7" t="n">
-        <v>57761</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,25 +1254,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103012</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1287,21 +1280,28 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stensta, Brobyborg, Upl</t>
+          <t>Barrskog S om Stensta, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>683542</v>
+        <v>683503</v>
       </c>
       <c r="R7" t="n">
-        <v>6616641</v>
+        <v>6616418</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 50435-2024 artfynd.xlsx
+++ b/artfynd/A 50435-2024 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124545084</v>
+        <v>124547663</v>
       </c>
       <c r="B5" t="n">
-        <v>57761</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1058,21 +1058,28 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stensta, Brobyborg, Upl</t>
+          <t>Barrskog S om Stensta, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683542</v>
+        <v>683503</v>
       </c>
       <c r="R5" t="n">
-        <v>6616641</v>
+        <v>6616418</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124545129</v>
+        <v>124545084</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>57761</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,21 +1154,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1180,13 +1187,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683517</v>
+        <v>683542</v>
       </c>
       <c r="R6" t="n">
-        <v>6616645</v>
+        <v>6616641</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1242,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124547663</v>
+        <v>124545129</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,25 +1261,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1280,31 +1287,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Barrskog S om Stensta, Brobyborg, Upl</t>
+          <t>Stensta, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>683503</v>
+        <v>683517</v>
       </c>
       <c r="R7" t="n">
-        <v>6616418</v>
+        <v>6616645</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 50435-2024 artfynd.xlsx
+++ b/artfynd/A 50435-2024 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124547663</v>
+        <v>124545129</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1058,31 +1058,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Barrskog S om Stensta, Brobyborg, Upl</t>
+          <t>Stensta, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683503</v>
+        <v>683517</v>
       </c>
       <c r="R5" t="n">
-        <v>6616418</v>
+        <v>6616645</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1249,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124545129</v>
+        <v>124547663</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,25 +1254,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1287,24 +1280,31 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stensta, Brobyborg, Upl</t>
+          <t>Barrskog S om Stensta, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>683517</v>
+        <v>683503</v>
       </c>
       <c r="R7" t="n">
-        <v>6616645</v>
+        <v>6616418</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 50435-2024 artfynd.xlsx
+++ b/artfynd/A 50435-2024 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124545129</v>
+        <v>124545084</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57761</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683517</v>
+        <v>683542</v>
       </c>
       <c r="R5" t="n">
-        <v>6616645</v>
+        <v>6616641</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124545084</v>
+        <v>124545129</v>
       </c>
       <c r="B6" t="n">
-        <v>57761</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,21 +1147,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103012</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1180,13 +1180,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683542</v>
+        <v>683517</v>
       </c>
       <c r="R6" t="n">
-        <v>6616641</v>
+        <v>6616645</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 50435-2024 artfynd.xlsx
+++ b/artfynd/A 50435-2024 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124545084</v>
+        <v>124545129</v>
       </c>
       <c r="B5" t="n">
-        <v>57761</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683542</v>
+        <v>683517</v>
       </c>
       <c r="R5" t="n">
-        <v>6616641</v>
+        <v>6616645</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124545129</v>
+        <v>124545084</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>57761</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,21 +1147,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1180,13 +1180,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683517</v>
+        <v>683542</v>
       </c>
       <c r="R6" t="n">
-        <v>6616645</v>
+        <v>6616641</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 50435-2024 artfynd.xlsx
+++ b/artfynd/A 50435-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1358,6 +1358,451 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125232986</v>
+      </c>
+      <c r="B8" t="n">
+        <v>103528</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Brobyborg, Brobyborg, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>683512</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6616657</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125232761</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98123</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Brobyborg, Brobyborg, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>683516</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6616568</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125232807</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98123</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Brobyborg, Brobyborg, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>683517</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6616583</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125232898</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100279</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Brobyborg, Brobyborg, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>683523</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6616628</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50435-2024 artfynd.xlsx
+++ b/artfynd/A 50435-2024 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124545129</v>
+        <v>124545084</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57761</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683517</v>
+        <v>683542</v>
       </c>
       <c r="R5" t="n">
-        <v>6616645</v>
+        <v>6616641</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124545084</v>
+        <v>124545129</v>
       </c>
       <c r="B6" t="n">
-        <v>57761</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,21 +1147,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103012</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1180,13 +1180,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683542</v>
+        <v>683517</v>
       </c>
       <c r="R6" t="n">
-        <v>6616641</v>
+        <v>6616645</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125232986</v>
+        <v>125232761</v>
       </c>
       <c r="B8" t="n">
-        <v>103528</v>
+        <v>98123</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,26 +1376,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>219862</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1403,16 +1403,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>683512</v>
+        <v>683516</v>
       </c>
       <c r="R8" t="n">
-        <v>6616657</v>
+        <v>6616568</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,10 +1476,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125232761</v>
+        <v>125232898</v>
       </c>
       <c r="B9" t="n">
-        <v>98123</v>
+        <v>100279</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,48 +1492,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>683516</v>
+        <v>683523</v>
       </c>
       <c r="R9" t="n">
-        <v>6616568</v>
+        <v>6616628</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1587,7 +1578,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125232807</v>
+        <v>125232820</v>
       </c>
       <c r="B10" t="n">
         <v>98123</v>
@@ -1622,7 +1613,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1703,10 +1694,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125232898</v>
+        <v>125232986</v>
       </c>
       <c r="B11" t="n">
-        <v>100279</v>
+        <v>103528</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,34 +1710,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>683523</v>
+        <v>683512</v>
       </c>
       <c r="R11" t="n">
-        <v>6616628</v>
+        <v>6616657</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 50435-2024 artfynd.xlsx
+++ b/artfynd/A 50435-2024 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124545084</v>
+        <v>124547663</v>
       </c>
       <c r="B5" t="n">
-        <v>57761</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1058,21 +1058,28 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stensta, Brobyborg, Upl</t>
+          <t>Barrskog S om Stensta, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683542</v>
+        <v>683503</v>
       </c>
       <c r="R5" t="n">
-        <v>6616641</v>
+        <v>6616418</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1242,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124547663</v>
+        <v>124545084</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>57761</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,25 +1261,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>103012</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1280,28 +1287,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Barrskog S om Stensta, Brobyborg, Upl</t>
+          <t>Stensta, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>683503</v>
+        <v>683542</v>
       </c>
       <c r="R7" t="n">
-        <v>6616418</v>
+        <v>6616641</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125232761</v>
+        <v>125232986</v>
       </c>
       <c r="B8" t="n">
-        <v>98123</v>
+        <v>103528</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,26 +1376,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219862</v>
+        <v>222412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1403,21 +1403,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>683516</v>
+        <v>683512</v>
       </c>
       <c r="R8" t="n">
-        <v>6616568</v>
+        <v>6616657</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125232898</v>
+        <v>125232820</v>
       </c>
       <c r="B9" t="n">
-        <v>100279</v>
+        <v>98123</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,34 +1487,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>683523</v>
+        <v>683517</v>
       </c>
       <c r="R9" t="n">
-        <v>6616628</v>
+        <v>6616583</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1578,7 +1587,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125232820</v>
+        <v>125232761</v>
       </c>
       <c r="B10" t="n">
         <v>98123</v>
@@ -1613,17 +1622,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1632,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>683517</v>
+        <v>683516</v>
       </c>
       <c r="R10" t="n">
-        <v>6616583</v>
+        <v>6616568</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1694,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125232986</v>
+        <v>125232898</v>
       </c>
       <c r="B11" t="n">
-        <v>103528</v>
+        <v>100279</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,43 +1719,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>683512</v>
+        <v>683523</v>
       </c>
       <c r="R11" t="n">
-        <v>6616657</v>
+        <v>6616628</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 50435-2024 artfynd.xlsx
+++ b/artfynd/A 50435-2024 artfynd.xlsx
@@ -1360,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125232986</v>
+        <v>125232761</v>
       </c>
       <c r="B8" t="n">
-        <v>103528</v>
+        <v>98123</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,26 +1376,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>219862</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1403,16 +1403,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>683512</v>
+        <v>683516</v>
       </c>
       <c r="R8" t="n">
-        <v>6616657</v>
+        <v>6616568</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1587,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125232761</v>
+        <v>125232898</v>
       </c>
       <c r="B10" t="n">
-        <v>98123</v>
+        <v>100279</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,48 +1608,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>683516</v>
+        <v>683523</v>
       </c>
       <c r="R10" t="n">
-        <v>6616568</v>
+        <v>6616628</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1703,10 +1694,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125232898</v>
+        <v>125232986</v>
       </c>
       <c r="B11" t="n">
-        <v>100279</v>
+        <v>103528</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,34 +1710,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>683523</v>
+        <v>683512</v>
       </c>
       <c r="R11" t="n">
-        <v>6616628</v>
+        <v>6616657</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 50435-2024 artfynd.xlsx
+++ b/artfynd/A 50435-2024 artfynd.xlsx
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124545129</v>
+        <v>124545084</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>57761</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,21 +1154,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1187,13 +1187,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683517</v>
+        <v>683542</v>
       </c>
       <c r="R6" t="n">
-        <v>6616645</v>
+        <v>6616641</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124545084</v>
+        <v>124545129</v>
       </c>
       <c r="B7" t="n">
-        <v>57761</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,21 +1265,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103012</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1298,13 +1298,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>683542</v>
+        <v>683517</v>
       </c>
       <c r="R7" t="n">
-        <v>6616641</v>
+        <v>6616645</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 50435-2024 artfynd.xlsx
+++ b/artfynd/A 50435-2024 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124547663</v>
+        <v>124545084</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>57761</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1058,28 +1058,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Barrskog S om Stensta, Brobyborg, Upl</t>
+          <t>Stensta, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683503</v>
+        <v>683542</v>
       </c>
       <c r="R5" t="n">
-        <v>6616418</v>
+        <v>6616641</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1138,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124545084</v>
+        <v>124547663</v>
       </c>
       <c r="B6" t="n">
-        <v>57761</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,25 +1143,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103012</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1176,21 +1169,28 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stensta, Brobyborg, Upl</t>
+          <t>Barrskog S om Stensta, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683542</v>
+        <v>683503</v>
       </c>
       <c r="R6" t="n">
-        <v>6616641</v>
+        <v>6616418</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1360,7 +1360,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125232761</v>
+        <v>125232820</v>
       </c>
       <c r="B8" t="n">
         <v>98123</v>
@@ -1395,17 +1395,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>683516</v>
+        <v>683517</v>
       </c>
       <c r="R8" t="n">
-        <v>6616568</v>
+        <v>6616583</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,10 +1476,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125232820</v>
+        <v>125232986</v>
       </c>
       <c r="B9" t="n">
-        <v>98123</v>
+        <v>103528</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,36 +1492,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219862</v>
+        <v>222412</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1530,10 +1525,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>683517</v>
+        <v>683512</v>
       </c>
       <c r="R9" t="n">
-        <v>6616583</v>
+        <v>6616657</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1592,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125232898</v>
+        <v>125232761</v>
       </c>
       <c r="B10" t="n">
-        <v>100279</v>
+        <v>98123</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,34 +1603,48 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>683523</v>
+        <v>683516</v>
       </c>
       <c r="R10" t="n">
-        <v>6616628</v>
+        <v>6616568</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1694,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125232986</v>
+        <v>125232898</v>
       </c>
       <c r="B11" t="n">
-        <v>103528</v>
+        <v>100279</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,43 +1719,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>683512</v>
+        <v>683523</v>
       </c>
       <c r="R11" t="n">
-        <v>6616657</v>
+        <v>6616628</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 50435-2024 artfynd.xlsx
+++ b/artfynd/A 50435-2024 artfynd.xlsx
@@ -1587,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125232761</v>
+        <v>125232898</v>
       </c>
       <c r="B10" t="n">
-        <v>98123</v>
+        <v>100279</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,48 +1603,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>683516</v>
+        <v>683523</v>
       </c>
       <c r="R10" t="n">
-        <v>6616568</v>
+        <v>6616628</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1703,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125232898</v>
+        <v>125232761</v>
       </c>
       <c r="B11" t="n">
-        <v>100279</v>
+        <v>98123</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,34 +1705,48 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>683523</v>
+        <v>683516</v>
       </c>
       <c r="R11" t="n">
-        <v>6616628</v>
+        <v>6616568</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 50435-2024 artfynd.xlsx
+++ b/artfynd/A 50435-2024 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124545084</v>
+        <v>124545129</v>
       </c>
       <c r="B5" t="n">
-        <v>57761</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683542</v>
+        <v>683517</v>
       </c>
       <c r="R5" t="n">
-        <v>6616641</v>
+        <v>6616645</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124547663</v>
+        <v>124545084</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>57761</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,25 +1143,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1169,28 +1169,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Barrskog S om Stensta, Brobyborg, Upl</t>
+          <t>Stensta, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683503</v>
+        <v>683542</v>
       </c>
       <c r="R6" t="n">
-        <v>6616418</v>
+        <v>6616641</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124545129</v>
+        <v>124547663</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,25 +1254,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1287,24 +1280,31 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stensta, Brobyborg, Upl</t>
+          <t>Barrskog S om Stensta, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>683517</v>
+        <v>683503</v>
       </c>
       <c r="R7" t="n">
-        <v>6616645</v>
+        <v>6616418</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125232820</v>
+        <v>125232986</v>
       </c>
       <c r="B8" t="n">
-        <v>98123</v>
+        <v>103528</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,36 +1376,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219862</v>
+        <v>222412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1414,10 +1409,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>683517</v>
+        <v>683512</v>
       </c>
       <c r="R8" t="n">
-        <v>6616583</v>
+        <v>6616657</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125232986</v>
+        <v>125232807</v>
       </c>
       <c r="B9" t="n">
-        <v>103528</v>
+        <v>98123</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,31 +1487,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222412</v>
+        <v>219862</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>683512</v>
+        <v>683517</v>
       </c>
       <c r="R9" t="n">
-        <v>6616657</v>
+        <v>6616583</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1587,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125232898</v>
+        <v>125232761</v>
       </c>
       <c r="B10" t="n">
-        <v>100279</v>
+        <v>98123</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,34 +1603,48 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>683523</v>
+        <v>683516</v>
       </c>
       <c r="R10" t="n">
-        <v>6616628</v>
+        <v>6616568</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1689,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125232761</v>
+        <v>125232898</v>
       </c>
       <c r="B11" t="n">
-        <v>98123</v>
+        <v>100279</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,48 +1719,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>683516</v>
+        <v>683523</v>
       </c>
       <c r="R11" t="n">
-        <v>6616568</v>
+        <v>6616628</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 50435-2024 artfynd.xlsx
+++ b/artfynd/A 50435-2024 artfynd.xlsx
@@ -1360,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125232986</v>
+        <v>125232761</v>
       </c>
       <c r="B8" t="n">
-        <v>103528</v>
+        <v>98291</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,26 +1376,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>219862</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1403,16 +1403,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>683512</v>
+        <v>683516</v>
       </c>
       <c r="R8" t="n">
-        <v>6616657</v>
+        <v>6616568</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,10 +1476,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125232807</v>
+        <v>125232986</v>
       </c>
       <c r="B9" t="n">
-        <v>98123</v>
+        <v>103700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,36 +1492,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219862</v>
+        <v>222412</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>683517</v>
+        <v>683512</v>
       </c>
       <c r="R9" t="n">
-        <v>6616583</v>
+        <v>6616657</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1587,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125232761</v>
+        <v>125232898</v>
       </c>
       <c r="B10" t="n">
-        <v>98123</v>
+        <v>100451</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,48 +1603,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>683516</v>
+        <v>683523</v>
       </c>
       <c r="R10" t="n">
-        <v>6616568</v>
+        <v>6616628</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1703,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125232898</v>
+        <v>125232820</v>
       </c>
       <c r="B11" t="n">
-        <v>100279</v>
+        <v>98291</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,34 +1705,48 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>683523</v>
+        <v>683517</v>
       </c>
       <c r="R11" t="n">
-        <v>6616628</v>
+        <v>6616583</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 50435-2024 artfynd.xlsx
+++ b/artfynd/A 50435-2024 artfynd.xlsx
@@ -1360,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125232761</v>
+        <v>125232986</v>
       </c>
       <c r="B8" t="n">
-        <v>98291</v>
+        <v>103700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,26 +1376,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219862</v>
+        <v>222412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1403,21 +1403,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>683516</v>
+        <v>683512</v>
       </c>
       <c r="R8" t="n">
-        <v>6616568</v>
+        <v>6616657</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125232986</v>
+        <v>125232761</v>
       </c>
       <c r="B9" t="n">
-        <v>103700</v>
+        <v>98291</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,26 +1487,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222412</v>
+        <v>219862</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1519,16 +1514,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>683512</v>
+        <v>683516</v>
       </c>
       <c r="R9" t="n">
-        <v>6616657</v>
+        <v>6616568</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1587,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125232898</v>
+        <v>125232820</v>
       </c>
       <c r="B10" t="n">
-        <v>100451</v>
+        <v>98291</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,34 +1603,48 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>683523</v>
+        <v>683517</v>
       </c>
       <c r="R10" t="n">
-        <v>6616628</v>
+        <v>6616583</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1689,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125232820</v>
+        <v>125232898</v>
       </c>
       <c r="B11" t="n">
-        <v>98291</v>
+        <v>100451</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,48 +1719,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>683517</v>
+        <v>683523</v>
       </c>
       <c r="R11" t="n">
-        <v>6616583</v>
+        <v>6616628</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 50435-2024 artfynd.xlsx
+++ b/artfynd/A 50435-2024 artfynd.xlsx
@@ -1360,15 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125232986</v>
+        <v>125232761</v>
       </c>
       <c r="B8" t="n">
-        <v>103700</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,26 +1371,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>219862</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1403,16 +1398,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>683512</v>
+        <v>683516</v>
       </c>
       <c r="R8" t="n">
-        <v>6616657</v>
+        <v>6616568</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,15 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125232761</v>
+        <v>125232898</v>
       </c>
       <c r="B9" t="n">
-        <v>98291</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100506</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,48 +1482,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>683516</v>
+        <v>683523</v>
       </c>
       <c r="R9" t="n">
-        <v>6616568</v>
+        <v>6616628</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1587,15 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125232820</v>
+        <v>125232986</v>
       </c>
       <c r="B10" t="n">
-        <v>98291</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103755</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1603,36 +1579,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219862</v>
+        <v>222412</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1641,10 +1612,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>683517</v>
+        <v>683512</v>
       </c>
       <c r="R10" t="n">
-        <v>6616583</v>
+        <v>6616657</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1703,15 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125232898</v>
+        <v>125232807</v>
       </c>
       <c r="B11" t="n">
-        <v>100451</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1719,34 +1685,48 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>683523</v>
+        <v>683517</v>
       </c>
       <c r="R11" t="n">
-        <v>6616628</v>
+        <v>6616583</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 50435-2024 artfynd.xlsx
+++ b/artfynd/A 50435-2024 artfynd.xlsx
@@ -1363,7 +1363,7 @@
         <v>125232761</v>
       </c>
       <c r="B8" t="n">
-        <v>98346</v>
+        <v>98353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>125232898</v>
       </c>
       <c r="B9" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>125232986</v>
       </c>
       <c r="B10" t="n">
-        <v>103755</v>
+        <v>103762</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>125232807</v>
       </c>
       <c r="B11" t="n">
-        <v>98346</v>
+        <v>98353</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 50435-2024 artfynd.xlsx
+++ b/artfynd/A 50435-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112029998</v>
+        <v>128609089</v>
       </c>
       <c r="B2" t="n">
-        <v>102205</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88982</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>3297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Aprikosfingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Clavulinopsis luteoalba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Rea) Corner</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brobyborg, Upl</t>
+          <t>Barrskog S Stensta, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>683562</v>
+        <v>683468</v>
       </c>
       <c r="R2" t="n">
-        <v>6616629</v>
+        <v>6616636</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>07:38</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>07:38</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -788,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124092317</v>
+        <v>128609110</v>
       </c>
       <c r="B3" t="n">
-        <v>103528</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89098</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,48 +787,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>4388</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mönjevaxing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hygrocybe miniata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>N Brobyborg, Brobyborg, Upl</t>
+          <t>Barrskog N Lövsta, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>683540</v>
+        <v>683471</v>
       </c>
       <c r="R3" t="n">
-        <v>6616608</v>
+        <v>6616633</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,12 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,6 +858,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -904,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124090043</v>
+        <v>124547663</v>
       </c>
       <c r="B4" t="n">
-        <v>103528</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -942,26 +910,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sydost om Stensta, Brobyborg, Upl</t>
+          <t>Barrskog S om Stensta, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683552</v>
+        <v>683503</v>
       </c>
       <c r="R4" t="n">
-        <v>6616649</v>
+        <v>6616418</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,12 +958,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,15 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124545129</v>
+        <v>124545084</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1069,13 +1034,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683517</v>
+        <v>683542</v>
       </c>
       <c r="R5" t="n">
-        <v>6616645</v>
+        <v>6616641</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,15 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124545084</v>
+        <v>124545129</v>
       </c>
       <c r="B6" t="n">
-        <v>57761</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,21 +1107,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103012</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1180,13 +1140,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683542</v>
+        <v>683517</v>
       </c>
       <c r="R6" t="n">
-        <v>6616641</v>
+        <v>6616645</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1242,15 +1202,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124547663</v>
+        <v>124394172</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,50 +1213,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Barrskog S om Stensta, Brobyborg, Upl</t>
+          <t>Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>683503</v>
+        <v>683465</v>
       </c>
       <c r="R7" t="n">
-        <v>6616418</v>
+        <v>6616644</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,12 +1272,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,7 +1307,7 @@
         <v>125232761</v>
       </c>
       <c r="B8" t="n">
-        <v>98353</v>
+        <v>99141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125232898</v>
+        <v>125232807</v>
       </c>
       <c r="B9" t="n">
-        <v>100513</v>
+        <v>99141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,34 +1426,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brobyborg, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>683523</v>
+        <v>683517</v>
       </c>
       <c r="R9" t="n">
-        <v>6616628</v>
+        <v>6616583</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125232986</v>
+        <v>112029998</v>
       </c>
       <c r="B10" t="n">
-        <v>103762</v>
+        <v>104628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,29 +1554,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Brobyborg, Brobyborg, Upl</t>
+          <t>Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>683512</v>
+        <v>683563</v>
       </c>
       <c r="R10" t="n">
-        <v>6616657</v>
+        <v>6616628</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1642,12 +1592,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2023-09-10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2023-09-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1674,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125232807</v>
+        <v>124089910</v>
       </c>
       <c r="B11" t="n">
-        <v>98353</v>
+        <v>104628</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,48 +1645,48 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219862</v>
+        <v>222412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Brobyborg, Brobyborg, Upl</t>
+          <t>Blandskog sydost om Stensta, Brobyborg, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>683517</v>
+        <v>683587</v>
       </c>
       <c r="R11" t="n">
-        <v>6616583</v>
+        <v>6616679</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,12 +1713,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1782,6 +1742,639 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124090043</v>
+      </c>
+      <c r="B12" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sydost om Stensta, Brobyborg, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>683552</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6616649</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>124091502</v>
+      </c>
+      <c r="B13" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>N Brobyborg, Brobyborg, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>683486</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6616413</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124092317</v>
+      </c>
+      <c r="B14" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>N Brobyborg, Brobyborg, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>683540</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6616608</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124394160</v>
+      </c>
+      <c r="B15" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Brobyborg, Brobyborg, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>683465</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6616644</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125232986</v>
+      </c>
+      <c r="B16" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Brobyborg, Brobyborg, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>683512</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6616657</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125232898</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Brobyborg, Brobyborg, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>683523</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6616628</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
